--- a/queries/ICP_CMS_Interface_Clarification_Questions.xlsx
+++ b/queries/ICP_CMS_Interface_Clarification_Questions.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总 Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'问题单 Questions'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'问题单 Questions'!$A$1:$J$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'问题单 Questions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -645,7 +645,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>日期 Date：2026-10-14</t>
+          <t>日期 Date：2026-10-14（Q01–Q32）· 2026-10-27 增补 Q33–Q35</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2206,8 +2206,128 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="70" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Q33</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>配置同步接口 synwas（Interface Reference p.907–933）</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>synwas 的各 GET 接口读取的是 CMS 网关上次同步的副本。平台是否会定时自动执行 CTI / VDN 同步（synccti / synvdn）？周期多长？若不会，由谁在什么时候触发？本方倾向不调用 synvdn（它是写动作，会连带删除数据），请确认。</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>The synwas GET interfaces return the copy from the gateway's last synchronisation. Does the platform run CTI / VDN synchronisation (syncti / synvdn) automatically? At what interval? If not, who triggers it and when? We prefer not to call synvdn ourselves (it is a write operation that may cascade deletes); please confirm.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>若网关不自动同步，坐席、技能队列等参照数据会无声地停在旧版本，版本号也不再变化。</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>高 High</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>待答复 Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="70" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>synwas/versions</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>versions 返回的 VDN 版本号是否只在同步成功时递增？内容没有变化的一次同步是否也会递增？</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Does the VDN version returned by versions increase only when a synchronisation succeeds? Does a synchronisation that changes nothing also increase it?</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>本方以「版本变了但内容无差异」作为异常告警；若每次同步都递增，该告警会每次误报。</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>中 Medium</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>待答复 Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="70" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Q35</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>synwas/agents · roleId</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>agents 的 roleId 是 CMS 的权限角色（2 配置管理员 / 3 质检员 / 4 普通坐席 / 5 报表管理员）。坐席的业务角色——接警员、调度员、主管——在 ICP 的任何接口或字段中是否有体现？</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>roleId in agents is the CMS permission role (2 configuration admin / 3 QA / 4 agent / 5 report admin). Is the business role of an agent (call-taker, dispatcher, supervisor) reflected in any ICP interface or field?</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>按业务角色统计的报表需要这个属性；ICP 若没有，须由 MOI 在本系统的管理界面维护。</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>中 Medium</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>待答复 Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J41"/>
   <mergeCells count="5">
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A22:J22"/>
@@ -2216,7 +2336,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J3:J41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待答复 Open,已答复 Answered,需进一步讨论 Needs discussion"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2263,11 +2383,11 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <f>COUNTIF('问题单 Questions'!$F$2:$F$38,A2)</f>
+        <f>COUNTIF('问题单 Questions'!$F$2:$F$41,A2)</f>
         <v/>
       </c>
       <c r="C2" s="15">
-        <f>COUNTIFS('问题单 Questions'!$F$2:$F$38,A2,'问题单 Questions'!$J$2:$J$38,"已答复 Answered")</f>
+        <f>COUNTIFS('问题单 Questions'!$F$2:$F$41,A2,'问题单 Questions'!$J$2:$J$41,"已答复 Answered")</f>
         <v/>
       </c>
     </row>
@@ -2278,11 +2398,11 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <f>COUNTIF('问题单 Questions'!$F$2:$F$38,A3)</f>
+        <f>COUNTIF('问题单 Questions'!$F$2:$F$41,A3)</f>
         <v/>
       </c>
       <c r="C3" s="15">
-        <f>COUNTIFS('问题单 Questions'!$F$2:$F$38,A3,'问题单 Questions'!$J$2:$J$38,"已答复 Answered")</f>
+        <f>COUNTIFS('问题单 Questions'!$F$2:$F$41,A3,'问题单 Questions'!$J$2:$J$41,"已答复 Answered")</f>
         <v/>
       </c>
     </row>
@@ -2293,11 +2413,11 @@
         </is>
       </c>
       <c r="B4" s="15">
-        <f>COUNTIF('问题单 Questions'!$F$2:$F$38,A4)</f>
+        <f>COUNTIF('问题单 Questions'!$F$2:$F$41,A4)</f>
         <v/>
       </c>
       <c r="C4" s="15">
-        <f>COUNTIFS('问题单 Questions'!$F$2:$F$38,A4,'问题单 Questions'!$J$2:$J$38,"已答复 Answered")</f>
+        <f>COUNTIFS('问题单 Questions'!$F$2:$F$41,A4,'问题单 Questions'!$J$2:$J$41,"已答复 Answered")</f>
         <v/>
       </c>
     </row>
